--- a/Defect Tracker Info.xlsx
+++ b/Defect Tracker Info.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{882F39A2-FEB5-43D8-AB43-F5E200A151D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A53A4AAC-A795-4F10-9AE9-B6EE59DC1F60}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C924EADB-DA21-435D-9F4F-C392DB0A2C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89926712-0E7B-4D91-967D-6DF06B549B60}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
   <si>
     <t>Sl No</t>
   </si>
@@ -104,13 +104,58 @@
   </si>
   <si>
     <t>Verified</t>
+  </si>
+  <si>
+    <t>Triage Agent classified a cosmetic UI bug report as High severity because it contained the word "fail" once in an unrelated sentence.</t>
+  </si>
+  <si>
+    <t>Added a minimum keyword-match threshold so a single incidental match no longer overrides the Medium default; only structural signals or multiple matches can elevate severity.</t>
+  </si>
+  <si>
+    <t>Log Analysis Agent extracted the wrong file name from a JS/Node stack trace when the line had a nested function call before the file path.</t>
+  </si>
+  <si>
+    <t>Rewrote the regex to prefer the file:line:col captured inside parentheses first, falling back to the generic pattern only if that fails.</t>
+  </si>
+  <si>
+    <t>Priority was not bumped for reports containing urgent language (e.g. "ASAP", "blocker") even though severity was already High.</t>
+  </si>
+  <si>
+    <t>Added an urgency-keyword check that bumps priority one level, without ever overriding the underlying severity classification.</t>
+  </si>
+  <si>
+    <t>Submitting a bug via /api/bugs/upload with a large multi-page PDF caused the Triage Agent to run on empty text because PDF extraction returned nothing for a scanned page.</t>
+  </si>
+  <si>
+    <t>Confirmed existing PDF-text validation already raises a clear error for non-extractable PDFs; added a test case to the seeded dataset so this path is covered going forward.</t>
+  </si>
+  <si>
+    <t>Orchestrator ran both agents twice for a single upload when multiple files were attached, doubling analysis time per request.</t>
+  </si>
+  <si>
+    <t>Fixed the upload loop so run_orchestration() is called exactly once per file, not once per file plus once for the batch.</t>
+  </si>
+  <si>
+    <t>AgentAnalysis record failed to save when a bug report contained only a Java stack trace with no message text, since log_message was treated as required.</t>
+  </si>
+  <si>
+    <t>Made log_message nullable in the DB model to match the Log Analysis Agent output, which can legitimately return None.</t>
+  </si>
+  <si>
+    <t>History modal on the frontend showed "Not available for this submission" for agent analysis even on bugs that had been analyzed, due to a mismatched bug id in the fetch URL.</t>
+  </si>
+  <si>
+    <t>Fixed the frontend to use the internal id (not bug_id) when calling GET /api/bugs/{id}/analysis.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -157,6 +202,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF003366"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -196,10 +253,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -218,9 +276,16 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{28E3A52C-7A7C-43CD-A2F4-BFA210AB3814}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -233,6 +298,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -816,95 +885,249 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="9">
+        <v>46218</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="9">
+        <v>46218</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="6"/>
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="9">
+        <v>46219</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="8">
+        <v>2</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="9">
+        <v>46219</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="6"/>
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="9">
+        <v>46220</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="9">
+        <v>46220</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="9">
+        <v>46222</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="9">
+        <v>46223</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="6"/>
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="9">
+        <v>46223</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="9">
+        <v>46224</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="9">
+        <v>46224</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="9">
+        <v>46224</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="6"/>
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="9">
+        <v>46225</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="9">
+        <v>46225</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>

--- a/Defect Tracker Info.xlsx
+++ b/Defect Tracker Info.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ea22cc3b98a8f61/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{C924EADB-DA21-435D-9F4F-C392DB0A2C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89926712-0E7B-4D91-967D-6DF06B549B60}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{C7116516-C309-488D-B097-FAFE8802658B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71230CCF-2DE2-48B9-8B0A-0BF59FF9BFD0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="62">
   <si>
     <t>Sl No</t>
   </si>
@@ -146,6 +146,66 @@
   </si>
   <si>
     <t>Fixed the frontend to use the internal id (not bug_id) when calling GET /api/bugs/{id}/analysis.</t>
+  </si>
+  <si>
+    <t>Root Cause Agent returned a hypothesis even when the historical defect knowledge base table was empty, instead of a clear fallback message.</t>
+  </si>
+  <si>
+    <t>Added an explicit empty-KB check that returns a zero-confidence fallback hypothesis with an empty evidence list.</t>
+  </si>
+  <si>
+    <t>TF-IDF similarity index treated stopword-only bug titles as valid documents, producing meaningless top matches.</t>
+  </si>
+  <si>
+    <t>Confirmed stopword filtering already excludes these terms; added a guard so empty token vectors return zero similarity instead of a false match.</t>
+  </si>
+  <si>
+    <t>Duplicate Detection Agent returned the bug being analyzed as its own duplicate match on re-analysis.</t>
+  </si>
+  <si>
+    <t>Passed exclude_bug_db_id through to the duplicate search so the current submission is filtered out of its own candidate corpus.</t>
+  </si>
+  <si>
+    <t>Duplicate matches list included very low similarity noise results from short, generic bug titles.</t>
+  </si>
+  <si>
+    <t>Added a similarity threshold filter so only matches above the minimum cutoff are surfaced to the dashboard.</t>
+  </si>
+  <si>
+    <t>Remediation Agent duplicated the same recommendation twice when both a strong duplicate match and a high-confidence root cause pointed to the same fix.</t>
+  </si>
+  <si>
+    <t>Added step de-duplication while preserving priority order, so repeated recommendations collapse into one entry.</t>
+  </si>
+  <si>
+    <t>Remediation Agent's confidence score could exceed the confidence of its weakest grounding input, overstating certainty.</t>
+  </si>
+  <si>
+    <t>Capped remediation confidence to a blend of duplicate and root cause confidence so it never overstates certainty beyond its inputs.</t>
+  </si>
+  <si>
+    <t>Structured Findings Dashboard showed a blank section instead of a message when no historical evidence or duplicate matches were found.</t>
+  </si>
+  <si>
+    <t>Added explicit empty-state messages for the Root Cause and Duplicate Bugs sections in the dashboard renderer.</t>
+  </si>
+  <si>
+    <t>History detail modal failed to render the Root Cause, Duplicate, and Remediation sections, showing only Triage and Log Analysis.</t>
+  </si>
+  <si>
+    <t>Updated the modal to call the shared renderDashboard() function so all five agent sections render consistently with the live preview.</t>
+  </si>
+  <si>
+    <t>Orchestrator queried the full bug_submissions table for every duplicate search, causing slow response times as submission history grew.</t>
+  </si>
+  <si>
+    <t>Added a capped limit on the prior-submissions query so duplicate search corpus size stays bounded on large datasets.</t>
+  </si>
+  <si>
+    <t>Best-practice playbook lookup crashed with a KeyError when Triage classified a report as an unrecognized component string.</t>
+  </si>
+  <si>
+    <t>Added a fallback to the Unclassified playbook whenever the component is not one of the defined playbook keys.</t>
   </si>
 </sst>
 </file>
@@ -257,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -282,6 +342,12 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -298,10 +364,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="17.54296875" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.1796875" style="4" bestFit="1" customWidth="1"/>
@@ -1130,82 +1192,354 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="11">
+        <v>46227</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="10">
+        <v>3</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="11">
+        <v>46227</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="6"/>
+      <c r="A16" s="10">
+        <v>15</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="11">
+        <v>46228</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="10">
+        <v>3</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="11">
+        <v>46228</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="6"/>
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="11">
+        <v>46228</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="11">
+        <v>46229</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="6"/>
+      <c r="A18" s="10">
+        <v>17</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="11">
+        <v>46229</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="10">
+        <v>3</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="11">
+        <v>46230</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="11">
+        <v>46230</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="10">
+        <v>3</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="11">
+        <v>46230</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="6"/>
+      <c r="A20" s="10">
+        <v>19</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="11">
+        <v>46231</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="10">
+        <v>3</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I20" s="11">
+        <v>46231</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="93" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="11">
+        <v>46231</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="10">
+        <v>3</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21" s="11">
+        <v>46232</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="108.5" x14ac:dyDescent="0.3">
+      <c r="A22" s="10">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="11">
+        <v>46232</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="10">
+        <v>3</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="11">
+        <v>46233</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="108.5" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="11">
+        <v>46233</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="10">
+        <v>3</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I23" s="11">
+        <v>46233</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="93" x14ac:dyDescent="0.3">
+      <c r="A24" s="10">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="11">
+        <v>46234</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="10">
+        <v>3</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="11">
+        <v>46234</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
